--- a/RoboMasterBoard/bom/RoboMasterBoard.xlsx
+++ b/RoboMasterBoard/bom/RoboMasterBoard.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\RoboMasterBoard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\Robocon2025-PCB\RoboMasterBoard\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC420686-2031-4A2D-AB70-458ED3A4E6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20EB8BA9-AB6C-4132-A82D-76EA130296D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{B7852339-0C57-462D-A5A6-BEED14B0BCB7}"/>
+    <workbookView xWindow="270" yWindow="3510" windowWidth="28530" windowHeight="7485" xr2:uid="{BFAA156D-E52A-4366-850B-92D15DC067B7}"/>
   </bookViews>
   <sheets>
     <sheet name="RoboMasterBoard" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="124">
   <si>
     <t>Reference</t>
   </si>
@@ -92,6 +79,12 @@
     <t>1u</t>
   </si>
   <si>
+    <t>GRM188D71H105ME01W</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188D71H105ME01W/22528412</t>
+  </si>
+  <si>
     <t>C10,C11</t>
   </si>
   <si>
@@ -176,15 +169,6 @@
     <t>https://www.digikey.jp/ja/products/detail/murata-electronics/BLM18KG601SN1D/1982766</t>
   </si>
   <si>
-    <t>H1,H2,H3,H4</t>
-  </si>
-  <si>
-    <t>MountingHole_Pad</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
@@ -233,12 +217,6 @@
     <t>https://www.digikey.jp/ja/products/detail/jst-sales-america-inc/S02B-PASK-2/926753</t>
   </si>
   <si>
-    <t>JP1,JP2</t>
-  </si>
-  <si>
-    <t>SolderJumper_2_Open</t>
-  </si>
-  <si>
     <t>R1,R2,R3,R4,R5,R6,R7,R8</t>
   </si>
   <si>
@@ -257,7 +235,7 @@
     <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ431/4051257?s=N4IgjCBcoCwGxVAYygMwIYBsDOBTANCAPZQDaIA7ABwAMATCALqEAOALlCAMpsBOAlgDsA5iAC%2BhMAE4qUxCBSQMOAsTIgaTCSDo0qAVnmLleQiUjkYAZhoACAPIALALbYmrDpBABVQfzb2qACyuOjYAK68uOKEALRy0ApQfOGq5uQQjNqxDImKKWnqhllxEHloWKZqFiBU8FpxMEYVKmbqVnUUCFnaueSAgwyAwwyA6wyArUaA6UZaQA</t>
   </si>
   <si>
-    <t>R10</t>
+    <t>R10,R23</t>
   </si>
   <si>
     <t>10k</t>
@@ -320,9 +298,6 @@
     <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ301/1762729</t>
   </si>
   <si>
-    <t>R23</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -413,31 +388,10 @@
     <t>Crystal_GND2</t>
   </si>
   <si>
-    <t>XRCGB32M000F1SADR0</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/XRCGB32M000F1SADR0/21662918?s=N4IgTCBcDaIBoCUDCBxAQgZjAWQAz4DEBGAZQEEARBXEAXQF8g</t>
-  </si>
-  <si>
-    <t>Price*Qty</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>合計</t>
-    <rPh sb="0" eb="2">
-      <t>ゴウケイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188D71H105ME01W/22528412</t>
-  </si>
-  <si>
-    <t>GRM188D71H105ME01W</t>
+    <t>XRCGB26M000F1SADR0</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/XRCGB26M000F1SADR0/21662900?s=N4IgTCBcDaIBoCUDCBxAQmAbAWQAz4DEBGAZQEEARBXEAXQF8g</t>
   </si>
 </sst>
 </file>
@@ -1411,15 +1365,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CAC5C8-BACD-4244-9A45-8C91426CBFED}">
-  <dimension ref="A1:G37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E8F50C8-69ED-4D65-870A-5BA83484053C}">
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="4" max="4" width="22.75" customWidth="1"/>
-    <col min="5" max="5" width="21.75" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1438,11 +1388,8 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1461,12 +1408,8 @@
       <c r="F2">
         <v>30</v>
       </c>
-      <c r="G2">
-        <f>F2*B2</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1485,12 +1428,8 @@
       <c r="F3">
         <v>19</v>
       </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G35" si="0">F3*B3</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1509,12 +1448,8 @@
       <c r="F4">
         <v>36</v>
       </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1525,744 +1460,553 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>47</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>16</v>
       </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>48</v>
       </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>53</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>212</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>30</v>
       </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>20</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12">
         <v>16</v>
       </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14">
-        <v>81</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
         <v>62</v>
       </c>
-      <c r="G15">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F16">
-        <v>110</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" t="s">
-        <v>63</v>
+      <c r="C17">
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F17">
-        <v>41</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>328</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18" t="s">
-        <v>67</v>
+      <c r="C18" s="1">
+        <v>420430</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+      <c r="F18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19">
-        <v>8</v>
-      </c>
-      <c r="C19">
-        <v>80</v>
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F19">
         <v>22</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="0"/>
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>420430</v>
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F20">
         <v>22</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F21">
         <v>22</v>
       </c>
-      <c r="G21">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F22">
         <v>22</v>
       </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F23">
         <v>22</v>
       </c>
-      <c r="G23">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>86</v>
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>300</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F24">
         <v>22</v>
       </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25">
-        <v>600</v>
+      <c r="C25" t="s">
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F25">
         <v>22</v>
       </c>
-      <c r="G25">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26">
-        <v>300</v>
+      <c r="C26" t="s">
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F26">
-        <v>22</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="F27">
-        <v>22</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F28">
-        <v>22</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F29">
-        <v>87</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F30">
-        <v>458</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="0"/>
-        <v>458</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F31">
-        <v>63</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F32">
-        <v>1348</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="0"/>
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33">
-        <v>202</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="0"/>
-        <v>404</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34">
-        <v>244</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="0"/>
-        <v>244</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" t="s">
-        <v>127</v>
-      </c>
-      <c r="F35">
-        <v>52</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="F37" t="s">
-        <v>130</v>
-      </c>
-      <c r="G37">
-        <f>SUM(G2:G35)</f>
-        <v>5031</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
